--- a/Painel CRM - Junho.xlsx
+++ b/Painel CRM - Junho.xlsx
@@ -1,167 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D28D88E1957AB5299FE540226AA26260132FC841" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{503021E9-35EC-4AAA-A900-8A0AC7DA51B6}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Painel Geral - Abril" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Painel Geral - Maio " state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Painel Geral - Junho" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Ariane" state="hidden" r:id="rId7"/>
-    <sheet sheetId="5" name="Camila" state="hidden" r:id="rId8"/>
-    <sheet sheetId="6" name="Cristielen" state="hidden" r:id="rId9"/>
-    <sheet sheetId="7" name="Natalia" state="hidden" r:id="rId10"/>
-    <sheet sheetId="8" name="Tatiana" state="hidden" r:id="rId11"/>
-    <sheet sheetId="9" name="Painel Geral - Julho" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="FATURAMENTO RECUPERACAO" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Planilha1" state="hidden" r:id="rId14"/>
+    <sheet name="Painel Geral - Abril" sheetId="1" r:id="rId1"/>
+    <sheet name="Painel Geral - Maio " sheetId="2" r:id="rId2"/>
+    <sheet name="Painel Geral - Junho" sheetId="3" r:id="rId3"/>
+    <sheet name="Ariane" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Camila" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Cristielen" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Natalia" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Tatiana" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Painel Geral - Julho" sheetId="9" r:id="rId9"/>
+    <sheet name="FATURAMENTO RECUPERACAO" sheetId="10" r:id="rId10"/>
+    <sheet name="Planilha1" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Tatiana!$AA$2:$AH$2</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="P35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="R35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="P36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="L38" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="AP33" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AB35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AD35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AF35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AH35" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="AL32" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AL33" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="R34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="T34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="V34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="X34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="Z34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AB34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AD34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AF34" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="F35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="H35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="J35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="R35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="T35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="V35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="X35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="Z35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AB35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AD35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AF35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AP35" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="F36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="H36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="J36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="R36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="AP36" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="R37" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -770,14 +634,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1140,99 +1004,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AR40"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2"/>
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="H2"/>
       <c r="I2">
         <v>6</v>
       </c>
-      <c r="J2"/>
       <c r="K2">
         <v>7</v>
       </c>
-      <c r="L2"/>
       <c r="M2">
         <v>8</v>
       </c>
-      <c r="N2"/>
       <c r="O2">
         <v>9</v>
       </c>
-      <c r="P2"/>
       <c r="Q2">
         <v>10</v>
       </c>
-      <c r="R2"/>
       <c r="S2">
         <v>13</v>
       </c>
-      <c r="T2"/>
       <c r="U2">
         <v>14</v>
       </c>
-      <c r="V2"/>
       <c r="W2">
         <v>15</v>
       </c>
-      <c r="X2"/>
       <c r="Y2">
         <v>16</v>
       </c>
-      <c r="Z2"/>
       <c r="AA2">
         <v>17</v>
       </c>
-      <c r="AB2"/>
       <c r="AC2">
         <v>20</v>
       </c>
-      <c r="AD2"/>
       <c r="AE2">
         <v>22</v>
       </c>
-      <c r="AF2"/>
       <c r="AG2">
         <v>23</v>
       </c>
-      <c r="AH2"/>
       <c r="AI2">
         <v>24</v>
       </c>
-      <c r="AJ2"/>
       <c r="AK2">
         <v>27</v>
       </c>
-      <c r="AL2"/>
       <c r="AM2">
         <v>28</v>
       </c>
-      <c r="AN2"/>
       <c r="AO2">
         <v>29</v>
       </c>
-      <c r="AP2"/>
       <c r="AQ2">
         <v>30</v>
       </c>
-      <c r="AR2"/>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1366,7 +1207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1377,7 +1218,7 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -1500,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1511,7 +1352,7 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1634,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1645,7 +1486,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1768,7 +1609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1902,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2036,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2170,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2179,7 +2020,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2188,18 +2029,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -2246,7 +2081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2270,7 +2105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2294,7 +2129,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2318,7 +2153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2341,7 +2176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2361,11 +2196,11 @@
         <v>85</v>
       </c>
       <c r="G20">
-        <f>SUM(B20:F20)</f>
+        <f t="shared" ref="G20:G29" si="0">SUM(B20:F20)</f>
         <v>894</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2385,11 +2220,11 @@
         <v>27</v>
       </c>
       <c r="G21">
-        <f>SUM(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2409,11 +2244,11 @@
         <v>12</v>
       </c>
       <c r="G22">
-        <f>SUM(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2433,11 +2268,11 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <f>SUM(B23:F23)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2457,11 +2292,11 @@
         <v>3</v>
       </c>
       <c r="G24">
-        <f>SUM(B24:F24)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2481,11 +2316,11 @@
         <v>22</v>
       </c>
       <c r="G25">
-        <f>SUM(B25:F25)</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2505,11 +2340,11 @@
         <v>2</v>
       </c>
       <c r="G26">
-        <f>SUM(B26:F26)</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2529,11 +2364,11 @@
         <v>8</v>
       </c>
       <c r="G27">
-        <f>SUM(B27:F27)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2553,11 +2388,11 @@
         <v>22</v>
       </c>
       <c r="G28">
-        <f>SUM(B28:F28)</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2577,11 +2412,11 @@
         <v>179</v>
       </c>
       <c r="G29">
-        <f>SUM(B29:F29)</f>
+        <f t="shared" si="0"/>
         <v>1441</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2606,59 +2441,45 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
       <c r="E33">
         <v>15</v>
       </c>
-      <c r="F33"/>
       <c r="G33">
         <v>16</v>
       </c>
-      <c r="H33"/>
       <c r="I33">
         <v>17</v>
       </c>
-      <c r="J33"/>
       <c r="K33">
         <v>20</v>
       </c>
-      <c r="L33"/>
       <c r="M33">
         <v>22</v>
       </c>
-      <c r="N33"/>
       <c r="O33">
         <v>23</v>
       </c>
-      <c r="P33"/>
       <c r="Q33">
         <v>24</v>
       </c>
-      <c r="R33"/>
       <c r="S33">
         <v>27</v>
       </c>
-      <c r="T33"/>
       <c r="U33">
         <v>28</v>
       </c>
-      <c r="V33"/>
       <c r="W33">
         <v>29</v>
       </c>
-      <c r="X33"/>
       <c r="Y33">
         <v>30</v>
       </c>
-      <c r="Z33"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -2738,7 +2559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2750,8 +2571,8 @@
         <v>295</v>
       </c>
       <c r="D35">
-        <f>C35/B35</f>
-        <v>0.8194444444444444</v>
+        <f t="shared" ref="D35:D40" si="1">C35/B35</f>
+        <v>0.81944444444444442</v>
       </c>
       <c r="E35">
         <v>33</v>
@@ -2820,7 +2641,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -2832,8 +2653,8 @@
         <v>185</v>
       </c>
       <c r="D36">
-        <f>C36/B36</f>
-        <v>0.9390862944162437</v>
+        <f t="shared" si="1"/>
+        <v>0.93908629441624369</v>
       </c>
       <c r="E36">
         <v>18</v>
@@ -2902,7 +2723,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -2914,7 +2735,7 @@
         <v>218</v>
       </c>
       <c r="D37">
-        <f>C37/B37</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E37">
@@ -2984,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -2996,7 +2817,7 @@
         <v>190</v>
       </c>
       <c r="D38">
-        <f>C38/B38</f>
+        <f t="shared" si="1"/>
         <v>1.0160427807486632</v>
       </c>
       <c r="E38">
@@ -3066,7 +2887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -3078,7 +2899,7 @@
         <v>115</v>
       </c>
       <c r="D39">
-        <f>C39/B39</f>
+        <f t="shared" si="1"/>
         <v>1.0267857142857142</v>
       </c>
       <c r="E39">
@@ -3148,7 +2969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3161,146 +2982,109 @@
         <v>1003</v>
       </c>
       <c r="D40">
-        <f>C40/B40</f>
-        <v>0.9338919925512105</v>
+        <f t="shared" si="1"/>
+        <v>0.93389199255121047</v>
       </c>
       <c r="E40">
-        <f>SUM(E35:E39)</f>
+        <f t="shared" ref="E40:Z40" si="2">SUM(E35:E39)</f>
         <v>100</v>
       </c>
       <c r="F40">
-        <f>SUM(F35:F39)</f>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="G40">
-        <f>SUM(G35:G39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="H40">
-        <f>SUM(H35:H39)</f>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="I40">
-        <f>SUM(I35:I39)</f>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="J40">
-        <f>SUM(J35:J39)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="K40">
-        <f>SUM(K35:K39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="L40">
-        <f>SUM(L35:L39)</f>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="M40">
-        <f>SUM(M35:M39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="N40">
-        <f>SUM(N35:N39)</f>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="O40">
-        <f>SUM(O35:O39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="P40">
-        <f>SUM(P35:P39)</f>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="Q40">
-        <f>SUM(Q35:Q39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="R40">
-        <f>SUM(R35:R39)</f>
+        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="S40">
-        <f>SUM(S35:S39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="T40">
-        <f>SUM(T35:T39)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="U40">
-        <f>SUM(U35:U39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="V40">
-        <f>SUM(V35:V39)</f>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="W40">
-        <f>SUM(W35:W39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="X40">
-        <f>SUM(X35:X39)</f>
+        <f t="shared" si="2"/>
         <v>124</v>
       </c>
       <c r="Y40">
-        <f>SUM(Y35:Y39)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="Z40">
-        <f>SUM(Z35:Z39)</f>
+        <f t="shared" si="2"/>
         <v>124</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="Y33:Z33"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C266"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>182</v>
       </c>
@@ -3311,7 +3095,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3322,7 +3106,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3333,7 +3117,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3344,7 +3128,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -3355,7 +3139,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -3366,7 +3150,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -3377,7 +3161,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3388,7 +3172,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3399,7 +3183,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3410,7 +3194,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3421,7 +3205,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3432,7 +3216,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -3443,7 +3227,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -3454,7 +3238,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -3465,7 +3249,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -3476,7 +3260,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -3487,7 +3271,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -3498,7 +3282,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3509,7 +3293,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -3520,7 +3304,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -3531,7 +3315,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -3542,7 +3326,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -3553,7 +3337,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -3564,7 +3348,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -3575,7 +3359,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -3586,7 +3370,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -3597,7 +3381,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -3608,7 +3392,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -3619,7 +3403,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -3630,7 +3414,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -3641,7 +3425,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -3652,7 +3436,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -3663,7 +3447,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -3674,7 +3458,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -3685,7 +3469,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -3696,7 +3480,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -3707,7 +3491,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -3718,7 +3502,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -3729,7 +3513,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -3740,7 +3524,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -3751,7 +3535,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -3762,7 +3546,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -3773,7 +3557,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3784,7 +3568,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -3795,7 +3579,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -3806,7 +3590,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -3817,7 +3601,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -3828,7 +3612,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -3839,7 +3623,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -3850,7 +3634,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -3861,7 +3645,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -3872,7 +3656,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -3883,7 +3667,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -3894,7 +3678,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -3905,7 +3689,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>85</v>
       </c>
@@ -3916,7 +3700,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -3927,7 +3711,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -3938,7 +3722,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -3949,7 +3733,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -3960,7 +3744,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -3971,7 +3755,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3982,7 +3766,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3993,7 +3777,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -4004,7 +3788,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -4015,7 +3799,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -4026,7 +3810,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -4037,7 +3821,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -4048,7 +3832,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -4059,7 +3843,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -4070,7 +3854,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -4081,7 +3865,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -4092,7 +3876,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -4103,7 +3887,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +3898,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -4125,7 +3909,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -4136,7 +3920,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -4147,7 +3931,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -4158,7 +3942,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>85</v>
       </c>
@@ -4169,7 +3953,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -4180,7 +3964,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -4191,7 +3975,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -4202,7 +3986,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -4213,7 +3997,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -4224,7 +4008,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -4235,7 +4019,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -4246,7 +4030,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>7</v>
       </c>
@@ -4257,7 +4041,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>7</v>
       </c>
@@ -4268,7 +4052,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>7</v>
       </c>
@@ -4279,7 +4063,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>7</v>
       </c>
@@ -4290,7 +4074,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>7</v>
       </c>
@@ -4301,7 +4085,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -4312,7 +4096,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -4323,7 +4107,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -4334,7 +4118,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -4345,7 +4129,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -4356,7 +4140,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -4367,7 +4151,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -4378,7 +4162,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -4389,7 +4173,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -4400,7 +4184,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -4411,7 +4195,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>8</v>
       </c>
@@ -4422,7 +4206,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -4433,7 +4217,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -4444,7 +4228,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -4455,7 +4239,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -4466,7 +4250,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -4477,7 +4261,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -4488,7 +4272,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -4499,7 +4283,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -4510,7 +4294,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -4521,7 +4305,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -4532,7 +4316,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -4543,7 +4327,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -4554,7 +4338,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -4565,7 +4349,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -4576,7 +4360,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -4587,7 +4371,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -4598,7 +4382,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>8</v>
       </c>
@@ -4609,7 +4393,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>8</v>
       </c>
@@ -4620,7 +4404,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -4631,7 +4415,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -4642,7 +4426,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>85</v>
       </c>
@@ -4653,7 +4437,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -4664,7 +4448,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>85</v>
       </c>
@@ -4675,7 +4459,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>85</v>
       </c>
@@ -4686,7 +4470,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -4697,7 +4481,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>85</v>
       </c>
@@ -4708,7 +4492,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>85</v>
       </c>
@@ -4719,7 +4503,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>85</v>
       </c>
@@ -4730,7 +4514,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>85</v>
       </c>
@@ -4741,7 +4525,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>85</v>
       </c>
@@ -4752,7 +4536,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>85</v>
       </c>
@@ -4763,7 +4547,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>85</v>
       </c>
@@ -4774,7 +4558,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>85</v>
       </c>
@@ -4785,7 +4569,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>85</v>
       </c>
@@ -4796,7 +4580,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>85</v>
       </c>
@@ -4807,7 +4591,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>85</v>
       </c>
@@ -4818,7 +4602,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>85</v>
       </c>
@@ -4829,7 +4613,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>85</v>
       </c>
@@ -4840,7 +4624,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>85</v>
       </c>
@@ -4851,7 +4635,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>85</v>
       </c>
@@ -4862,7 +4646,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>85</v>
       </c>
@@ -4873,7 +4657,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>85</v>
       </c>
@@ -4884,7 +4668,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -4895,7 +4679,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -4906,7 +4690,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -4917,7 +4701,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -4928,7 +4712,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -4939,7 +4723,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -4950,7 +4734,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -4961,7 +4745,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -4972,7 +4756,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -4983,7 +4767,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -4994,7 +4778,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -5005,7 +4789,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -5016,7 +4800,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -5027,7 +4811,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -5038,7 +4822,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -5049,7 +4833,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -5060,7 +4844,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>32</v>
       </c>
@@ -5071,7 +4855,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>32</v>
       </c>
@@ -5082,7 +4866,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>32</v>
       </c>
@@ -5093,7 +4877,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>32</v>
       </c>
@@ -5104,7 +4888,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>32</v>
       </c>
@@ -5115,7 +4899,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>32</v>
       </c>
@@ -5126,7 +4910,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>8</v>
       </c>
@@ -5137,7 +4921,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -5148,7 +4932,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -5159,7 +4943,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -5170,7 +4954,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -5181,7 +4965,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -5192,7 +4976,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -5203,7 +4987,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -5214,7 +4998,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -5225,7 +5009,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -5236,7 +5020,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -5247,7 +5031,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -5258,7 +5042,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>8</v>
       </c>
@@ -5269,7 +5053,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -5280,7 +5064,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>8</v>
       </c>
@@ -5291,7 +5075,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>8</v>
       </c>
@@ -5302,7 +5086,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -5313,7 +5097,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>8</v>
       </c>
@@ -5324,7 +5108,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>8</v>
       </c>
@@ -5335,7 +5119,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>8</v>
       </c>
@@ -5346,7 +5130,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>8</v>
       </c>
@@ -5357,7 +5141,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>8</v>
       </c>
@@ -5368,7 +5152,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>8</v>
       </c>
@@ -5379,7 +5163,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>8</v>
       </c>
@@ -5390,7 +5174,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>8</v>
       </c>
@@ -5401,7 +5185,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>8</v>
       </c>
@@ -5412,7 +5196,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>8</v>
       </c>
@@ -5423,7 +5207,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>8</v>
       </c>
@@ -5434,7 +5218,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>85</v>
       </c>
@@ -5445,7 +5229,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>85</v>
       </c>
@@ -5456,7 +5240,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>85</v>
       </c>
@@ -5467,7 +5251,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>85</v>
       </c>
@@ -5478,7 +5262,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>85</v>
       </c>
@@ -5489,7 +5273,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>85</v>
       </c>
@@ -5500,7 +5284,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>85</v>
       </c>
@@ -5511,7 +5295,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>85</v>
       </c>
@@ -5522,7 +5306,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>85</v>
       </c>
@@ -5533,7 +5317,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -5544,7 +5328,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -5555,7 +5339,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -5566,7 +5350,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -5577,7 +5361,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -5588,7 +5372,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -5599,7 +5383,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -5610,7 +5394,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -5621,7 +5405,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -5632,7 +5416,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -5643,7 +5427,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -5654,7 +5438,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -5665,7 +5449,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -5676,7 +5460,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -5687,7 +5471,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>32</v>
       </c>
@@ -5698,7 +5482,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>32</v>
       </c>
@@ -5709,7 +5493,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>32</v>
       </c>
@@ -5720,7 +5504,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>7</v>
       </c>
@@ -5731,7 +5515,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>7</v>
       </c>
@@ -5742,7 +5526,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>7</v>
       </c>
@@ -5753,7 +5537,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>7</v>
       </c>
@@ -5764,7 +5548,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>7</v>
       </c>
@@ -5775,7 +5559,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>8</v>
       </c>
@@ -5786,7 +5570,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>8</v>
       </c>
@@ -5797,7 +5581,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>8</v>
       </c>
@@ -5808,7 +5592,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>8</v>
       </c>
@@ -5819,7 +5603,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>8</v>
       </c>
@@ -5830,7 +5614,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>8</v>
       </c>
@@ -5841,7 +5625,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>8</v>
       </c>
@@ -5852,7 +5636,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>8</v>
       </c>
@@ -5863,7 +5647,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>8</v>
       </c>
@@ -5874,7 +5658,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>8</v>
       </c>
@@ -5885,7 +5669,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>8</v>
       </c>
@@ -5896,7 +5680,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>8</v>
       </c>
@@ -5907,7 +5691,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>8</v>
       </c>
@@ -5918,7 +5702,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>8</v>
       </c>
@@ -5929,7 +5713,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>8</v>
       </c>
@@ -5940,7 +5724,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>8</v>
       </c>
@@ -5951,7 +5735,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -5962,7 +5746,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>32</v>
       </c>
@@ -5973,7 +5757,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>32</v>
       </c>
@@ -5984,7 +5768,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>32</v>
       </c>
@@ -5995,7 +5779,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>32</v>
       </c>
@@ -6006,7 +5790,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>32</v>
       </c>
@@ -6017,7 +5801,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>32</v>
       </c>
@@ -6028,7 +5812,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -6039,7 +5823,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -6050,7 +5834,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -6061,7 +5845,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -6072,7 +5856,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -6083,7 +5867,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -6094,7 +5878,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -6105,7 +5889,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -6116,7 +5900,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -6127,7 +5911,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -6138,7 +5922,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -6149,7 +5933,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -6160,7 +5944,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -6171,7 +5955,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -6182,7 +5966,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -6193,7 +5977,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>10</v>
       </c>
@@ -6204,7 +5988,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>10</v>
       </c>
@@ -6215,7 +5999,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>189</v>
       </c>
@@ -6227,21 +6011,21 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:M32"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>191</v>
       </c>
@@ -6261,8 +6045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6"/>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>64</v>
       </c>
@@ -6285,7 +6068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -6308,7 +6091,7 @@
         <v>41</v>
       </c>
       <c r="H7">
-        <f>SUM(C7:G7)</f>
+        <f t="shared" ref="H7:H16" si="0">SUM(C7:G7)</f>
         <v>418</v>
       </c>
       <c r="I7">
@@ -6316,8 +6099,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8"/>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -6337,13 +6119,11 @@
         <v>43</v>
       </c>
       <c r="H8">
-        <f>SUM(C8:G8)</f>
+        <f t="shared" si="0"/>
         <v>302</v>
       </c>
-      <c r="I8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -6363,13 +6143,11 @@
         <v>24</v>
       </c>
       <c r="H9">
-        <f>SUM(C9:G9)</f>
+        <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="I9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -6389,16 +6167,14 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <f>SUM(C10:G10)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="I10"/>
       <c r="L10" t="s">
         <v>193</v>
       </c>
-      <c r="M10"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>194</v>
       </c>
@@ -6421,7 +6197,7 @@
         <v>2</v>
       </c>
       <c r="H11">
-        <f>SUM(C11:G11)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="I11">
@@ -6435,8 +6211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12"/>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>72</v>
       </c>
@@ -6456,10 +6231,9 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <f>SUM(C12:G12)</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="I12"/>
       <c r="L12" t="s">
         <v>6</v>
       </c>
@@ -6467,8 +6241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>195</v>
       </c>
@@ -6488,10 +6261,9 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <f>SUM(C13:G13)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="I13"/>
       <c r="L13" t="s">
         <v>7</v>
       </c>
@@ -6499,8 +6271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14"/>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>24</v>
       </c>
@@ -6520,10 +6291,9 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <f>SUM(C14:G14)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I14"/>
       <c r="L14" t="s">
         <v>8</v>
       </c>
@@ -6531,8 +6301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>25</v>
       </c>
@@ -6552,10 +6321,9 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <f>SUM(C15:G15)</f>
-        <v>2</v>
-      </c>
-      <c r="I15"/>
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="L15" t="s">
         <v>9</v>
       </c>
@@ -6563,7 +6331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C16">
         <f>SUM(C7:C15)</f>
         <v>340</v>
@@ -6585,7 +6353,7 @@
         <v>124</v>
       </c>
       <c r="H16">
-        <f>SUM(C16:G16)</f>
+        <f t="shared" si="0"/>
         <v>1073</v>
       </c>
       <c r="L16" t="s">
@@ -6595,7 +6363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
         <v>11</v>
       </c>
@@ -6603,7 +6371,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>196</v>
       </c>
@@ -6623,8 +6391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>64</v>
       </c>
@@ -6649,9 +6416,8 @@
       <c r="L20" t="s">
         <v>197</v>
       </c>
-      <c r="M20"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>198</v>
       </c>
@@ -6674,7 +6440,7 @@
         <v>54</v>
       </c>
       <c r="H21">
-        <f>SUM(C21:G21)</f>
+        <f t="shared" ref="H21:H30" si="1">SUM(C21:G21)</f>
         <v>472</v>
       </c>
       <c r="I21">
@@ -6688,8 +6454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>17</v>
       </c>
@@ -6709,10 +6474,9 @@
         <v>13</v>
       </c>
       <c r="H22">
-        <f>SUM(C22:G22)</f>
+        <f t="shared" si="1"/>
         <v>139</v>
       </c>
-      <c r="I22"/>
       <c r="L22" t="s">
         <v>6</v>
       </c>
@@ -6720,8 +6484,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23"/>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>18</v>
       </c>
@@ -6741,10 +6504,9 @@
         <v>24</v>
       </c>
       <c r="H23">
-        <f>SUM(C23:G23)</f>
+        <f t="shared" si="1"/>
         <v>185</v>
       </c>
-      <c r="I23"/>
       <c r="L23" t="s">
         <v>7</v>
       </c>
@@ -6752,8 +6514,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>19</v>
       </c>
@@ -6773,10 +6534,9 @@
         <v>3</v>
       </c>
       <c r="H24">
-        <f>SUM(C24:G24)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="I24"/>
       <c r="L24" t="s">
         <v>8</v>
       </c>
@@ -6784,7 +6544,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>194</v>
       </c>
@@ -6807,7 +6567,7 @@
         <v>28</v>
       </c>
       <c r="H25">
-        <f>SUM(C25:G25)</f>
+        <f t="shared" si="1"/>
         <v>316</v>
       </c>
       <c r="I25">
@@ -6821,8 +6581,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26"/>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>72</v>
       </c>
@@ -6842,10 +6601,9 @@
         <v>19</v>
       </c>
       <c r="H26">
-        <f>SUM(C26:G26)</f>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="I26"/>
       <c r="L26" t="s">
         <v>10</v>
       </c>
@@ -6853,8 +6611,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27"/>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>195</v>
       </c>
@@ -6874,10 +6631,9 @@
         <v>15</v>
       </c>
       <c r="H27">
-        <f>SUM(C27:G27)</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="I27"/>
       <c r="L27" t="s">
         <v>11</v>
       </c>
@@ -6886,8 +6642,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28"/>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>24</v>
       </c>
@@ -6907,13 +6662,11 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <f>SUM(C28:G28)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="I28"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>25</v>
       </c>
@@ -6933,12 +6686,11 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <f>SUM(C29:G29)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="I29"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C30">
         <f>SUM(C21:C29)</f>
         <v>456</v>
@@ -6960,11 +6712,11 @@
         <v>157</v>
       </c>
       <c r="H30">
-        <f>SUM(C30:G30)</f>
+        <f t="shared" si="1"/>
         <v>1354</v>
       </c>
     </row>
-    <row r="32" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="G32" t="s">
         <v>199</v>
       </c>
@@ -6974,118 +6726,81 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="I11:I15"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="I25:I29"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:AR37"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2"/>
       <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2"/>
       <c r="I2">
         <v>6</v>
       </c>
-      <c r="J2"/>
       <c r="K2">
         <v>7</v>
       </c>
-      <c r="L2"/>
       <c r="M2">
         <v>8</v>
       </c>
-      <c r="N2"/>
       <c r="O2">
         <v>11</v>
       </c>
-      <c r="P2"/>
       <c r="Q2">
         <v>12</v>
       </c>
-      <c r="R2"/>
       <c r="S2">
         <v>13</v>
       </c>
-      <c r="T2"/>
       <c r="U2">
         <v>14</v>
       </c>
-      <c r="V2"/>
       <c r="W2">
         <v>15</v>
       </c>
-      <c r="X2"/>
       <c r="Y2">
         <v>18</v>
       </c>
-      <c r="Z2"/>
       <c r="AA2">
         <v>19</v>
       </c>
-      <c r="AB2"/>
       <c r="AC2">
         <v>20</v>
       </c>
-      <c r="AD2"/>
       <c r="AE2">
         <v>21</v>
       </c>
-      <c r="AF2"/>
       <c r="AG2">
         <v>22</v>
       </c>
-      <c r="AH2"/>
       <c r="AI2">
         <v>25</v>
       </c>
-      <c r="AJ2"/>
       <c r="AK2">
         <v>26</v>
       </c>
-      <c r="AL2"/>
       <c r="AM2">
         <v>27</v>
       </c>
-      <c r="AN2"/>
       <c r="AO2">
         <v>28</v>
       </c>
-      <c r="AP2"/>
       <c r="AQ2">
         <v>29</v>
       </c>
-      <c r="AR2"/>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7219,7 +6934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -7353,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -7487,7 +7202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7621,7 +7336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7755,7 +7470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7889,7 +7604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -8023,7 +7738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8032,7 +7747,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -8041,18 +7756,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -8075,7 +7784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -8099,7 +7808,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -8123,7 +7832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -8147,7 +7856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -8171,7 +7880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -8194,7 +7903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -8214,11 +7923,11 @@
         <v>125</v>
       </c>
       <c r="G20">
-        <f>SUM(B20:F20)</f>
+        <f t="shared" ref="G20:G26" si="0">SUM(B20:F20)</f>
         <v>1117</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -8238,11 +7947,11 @@
         <v>45</v>
       </c>
       <c r="G21">
-        <f>SUM(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -8262,11 +7971,11 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <f>SUM(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -8286,11 +7995,11 @@
         <v>4</v>
       </c>
       <c r="G23">
-        <f>SUM(B23:F23)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -8310,11 +8019,11 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <f>SUM(B24:F24)</f>
+        <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -8334,11 +8043,11 @@
         <v>4</v>
       </c>
       <c r="G25">
-        <f>SUM(B25:F25)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -8358,11 +8067,11 @@
         <v>2</v>
       </c>
       <c r="G26">
-        <f>SUM(B26:F26)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -8387,95 +8096,72 @@
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
       <c r="E30">
         <v>4</v>
       </c>
-      <c r="F30"/>
       <c r="G30">
         <v>5</v>
       </c>
-      <c r="H30"/>
       <c r="I30">
         <v>6</v>
       </c>
-      <c r="J30"/>
       <c r="K30">
         <v>7</v>
       </c>
-      <c r="L30"/>
       <c r="M30">
         <v>8</v>
       </c>
-      <c r="N30"/>
       <c r="O30">
         <v>11</v>
       </c>
-      <c r="P30"/>
       <c r="Q30">
         <v>12</v>
       </c>
-      <c r="R30"/>
       <c r="S30">
         <v>13</v>
       </c>
-      <c r="T30"/>
       <c r="U30">
         <v>14</v>
       </c>
-      <c r="V30"/>
       <c r="W30">
         <v>15</v>
       </c>
-      <c r="X30"/>
       <c r="Y30">
         <v>18</v>
       </c>
-      <c r="Z30"/>
       <c r="AA30">
         <v>19</v>
       </c>
-      <c r="AB30"/>
       <c r="AC30">
         <v>20</v>
       </c>
-      <c r="AD30"/>
       <c r="AE30">
         <v>21</v>
       </c>
-      <c r="AF30"/>
       <c r="AG30">
         <v>22</v>
       </c>
-      <c r="AH30"/>
       <c r="AI30">
         <v>25</v>
       </c>
-      <c r="AJ30"/>
       <c r="AK30">
         <v>26</v>
       </c>
-      <c r="AL30"/>
       <c r="AM30">
         <v>27</v>
       </c>
-      <c r="AN30"/>
       <c r="AO30">
         <v>28</v>
       </c>
-      <c r="AP30"/>
       <c r="AQ30">
         <v>29</v>
       </c>
-      <c r="AR30"/>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -8609,21 +8295,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>7</v>
       </c>
       <c r="B32">
-        <f>E32+G32+I32+K32+M32+O32+Q32+S32+U32+W32+Y32+AA32+AC32+AE32+AG32+AI32+AK32+AM32+AO32+AQ32</f>
+        <f t="shared" ref="B32:C36" si="1">E32+G32+I32+K32+M32+O32+Q32+S32+U32+W32+Y32+AA32+AC32+AE32+AG32+AI32+AK32+AM32+AO32+AQ32</f>
         <v>299</v>
       </c>
       <c r="C32">
-        <f>F32+H32+J32+L32+N32+P32+R32+T32+V32+X32+Z32+AB32+AD32+AF32+AH32+AJ32+AL32+AN32+AP32+AR32</f>
+        <f t="shared" si="1"/>
         <v>275</v>
       </c>
       <c r="D32">
-        <f>C32/B32</f>
-        <v>0.919732441471572</v>
+        <f t="shared" ref="D32:D37" si="2">C32/B32</f>
+        <v>0.91973244147157196</v>
       </c>
       <c r="E32">
         <v>15</v>
@@ -8747,20 +8433,20 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33">
-        <f>E33+G33+I33+K33+M33+O33+Q33+S33+U33+W33+Y33+AA33+AC33+AE33+AG33+AI33+AK33+AM33+AO33+AQ33</f>
+        <f t="shared" si="1"/>
         <v>257</v>
       </c>
       <c r="C33">
-        <f>F33+H33+J33+L33+N33+P33+R33+T33+V33+X33+Z33+AB33+AD33+AF33+AH33+AJ33+AL33+AN33+AP33+AR33</f>
+        <f t="shared" si="1"/>
         <v>344</v>
       </c>
       <c r="D33">
-        <f>C33/B33</f>
+        <f t="shared" si="2"/>
         <v>1.33852140077821</v>
       </c>
       <c r="E33">
@@ -8884,20 +8570,20 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34">
-        <f>E34+G34+I34+K34+M34+O34+Q34+S34+U34+W34+Y34+AA34+AC34+AE34+AG34+AI34+AK34+AM34+AO34+AQ34</f>
+        <f t="shared" si="1"/>
         <v>508</v>
       </c>
       <c r="C34">
-        <f>F34+H34+J34+L34+N34+P34+R34+T34+V34+X34+Z34+AB34+AD34+AF34+AH34+AJ34+AL34+AN34+AP34+AR34</f>
+        <f t="shared" si="1"/>
         <v>510</v>
       </c>
       <c r="D34">
-        <f>C34/B34</f>
+        <f t="shared" si="2"/>
         <v>1.0039370078740157</v>
       </c>
       <c r="E34">
@@ -9021,20 +8707,20 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
       <c r="B35">
-        <f>E35+G35+I35+K35+M35+O35+Q35+S35+U35+W35+Y35+AA35+AC35+AE35+AG35+AI35+AK35+AM35+AO35+AQ35</f>
+        <f t="shared" si="1"/>
         <v>326</v>
       </c>
       <c r="C35">
-        <f>F35+H35+J35+L35+N35+P35+R35+T35+V35+X35+Z35+AB35+AD35+AF35+AH35+AJ35+AL35+AN35+AP35+AR35</f>
+        <f t="shared" si="1"/>
         <v>331</v>
       </c>
       <c r="D35">
-        <f>C35/B35</f>
+        <f t="shared" si="2"/>
         <v>1.0153374233128833</v>
       </c>
       <c r="E35">
@@ -9158,20 +8844,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>10</v>
       </c>
       <c r="B36">
-        <f>E36+G36+I36+K36+M36+O36+Q36+S36+U36+W36+Y36+AA36+AC36+AE36+AG36+AI36+AK36+AM36+AO36+AQ36</f>
+        <f t="shared" si="1"/>
         <v>233</v>
       </c>
       <c r="C36">
-        <f>F36+H36+J36+L36+N36+P36+R36+T36+V36+X36+Z36+AB36+AD36+AF36+AH36+AJ36+AL36+AN36+AP36+AR36</f>
+        <f t="shared" si="1"/>
         <v>241</v>
       </c>
       <c r="D36">
-        <f>C36/B36</f>
+        <f t="shared" si="2"/>
         <v>1.0343347639484979</v>
       </c>
       <c r="E36">
@@ -9295,7 +8981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -9308,319 +8994,249 @@
         <v>1701</v>
       </c>
       <c r="D37">
-        <f>C37/B37</f>
+        <f t="shared" si="2"/>
         <v>1.0480591497227356</v>
       </c>
       <c r="E37">
-        <f>SUM(E32:E36)</f>
+        <f t="shared" ref="E37:AR37" si="3">SUM(E32:E36)</f>
         <v>95</v>
       </c>
       <c r="F37">
-        <f>SUM(F32:F36)</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="G37">
-        <f>SUM(G32:G36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="H37">
-        <f>SUM(H32:H36)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I37">
-        <f>SUM(I32:I36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="J37">
-        <f>SUM(J32:J36)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="K37">
-        <f>SUM(K32:K36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="L37">
-        <f>SUM(L32:L36)</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="M37">
-        <f>SUM(M32:M36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="N37">
-        <f>SUM(N32:N36)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="O37">
-        <f>SUM(O32:O36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="P37">
-        <f>SUM(P32:P36)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="Q37">
-        <f>SUM(Q32:Q36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="R37">
-        <f>SUM(R32:R36)</f>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="S37">
-        <f>SUM(S32:S36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="T37">
-        <f>SUM(T32:T36)</f>
+        <f t="shared" si="3"/>
         <v>102</v>
       </c>
       <c r="U37">
-        <f>SUM(U32:U36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="V37">
-        <f>SUM(V32:V36)</f>
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="W37">
-        <f>SUM(W32:W36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="X37">
-        <f>SUM(X32:X36)</f>
+        <f t="shared" si="3"/>
         <v>104</v>
       </c>
       <c r="Y37">
-        <f>SUM(Y32:Y36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="Z37">
-        <f>SUM(Z32:Z36)</f>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
       <c r="AA37">
-        <f>SUM(AA32:AA36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AB37">
-        <f>SUM(AB32:AB36)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="AC37">
-        <f>SUM(AC32:AC36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AD37">
-        <f>SUM(AD32:AD36)</f>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="AE37">
-        <f>SUM(AE32:AE36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AF37">
-        <f>SUM(AF32:AF36)</f>
+        <f t="shared" si="3"/>
         <v>77</v>
       </c>
       <c r="AG37">
-        <f>SUM(AG32:AG36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AH37">
-        <f>SUM(AH32:AH36)</f>
+        <f t="shared" si="3"/>
         <v>124</v>
       </c>
       <c r="AI37">
-        <f>SUM(AI32:AI36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AJ37">
-        <f>SUM(AJ32:AJ36)</f>
+        <f t="shared" si="3"/>
         <v>182</v>
       </c>
       <c r="AK37">
-        <f>SUM(AK32:AK36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AL37">
-        <f>SUM(AL32:AL36)</f>
+        <f t="shared" si="3"/>
         <v>201</v>
       </c>
       <c r="AM37">
-        <f>SUM(AM32:AM36)</f>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AN37">
-        <f>SUM(AN32:AN36)</f>
+        <f t="shared" si="3"/>
         <v>141</v>
       </c>
       <c r="AO37">
-        <f>SUM(AO32:AO36)</f>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="AP37">
-        <f>SUM(AP32:AP36)</f>
+        <f t="shared" si="3"/>
         <v>112</v>
       </c>
       <c r="AQ37">
-        <f>SUM(AQ32:AQ36)</f>
+        <f t="shared" si="3"/>
         <v>73</v>
       </c>
       <c r="AR37">
-        <f>SUM(AR32:AR36)</f>
+        <f t="shared" si="3"/>
         <v>141</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="AA30:AB30"/>
-    <mergeCell ref="AC30:AD30"/>
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AI30:AJ30"/>
-    <mergeCell ref="AK30:AL30"/>
-    <mergeCell ref="AM30:AN30"/>
-    <mergeCell ref="AO30:AP30"/>
-    <mergeCell ref="AQ30:AR30"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:AT37"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2"/>
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="H2"/>
       <c r="I2">
         <v>3</v>
       </c>
-      <c r="J2"/>
       <c r="K2">
         <v>5</v>
       </c>
-      <c r="L2"/>
       <c r="M2">
         <v>8</v>
       </c>
-      <c r="N2"/>
       <c r="O2">
         <v>9</v>
       </c>
-      <c r="P2"/>
       <c r="Q2">
         <v>10</v>
       </c>
-      <c r="R2"/>
       <c r="S2">
         <v>11</v>
       </c>
-      <c r="T2"/>
       <c r="U2">
         <v>12</v>
       </c>
-      <c r="V2"/>
       <c r="W2">
         <v>15</v>
       </c>
-      <c r="X2"/>
       <c r="Y2">
         <v>16</v>
       </c>
-      <c r="Z2"/>
       <c r="AA2">
         <v>17</v>
       </c>
-      <c r="AB2"/>
       <c r="AC2">
         <v>18</v>
       </c>
-      <c r="AD2"/>
       <c r="AE2">
         <v>19</v>
       </c>
-      <c r="AF2"/>
       <c r="AG2">
         <v>22</v>
       </c>
-      <c r="AH2"/>
       <c r="AI2">
         <v>23</v>
       </c>
-      <c r="AJ2"/>
       <c r="AK2">
         <v>24</v>
       </c>
-      <c r="AL2"/>
       <c r="AM2">
         <v>25</v>
       </c>
-      <c r="AN2"/>
       <c r="AO2">
         <v>26</v>
       </c>
-      <c r="AP2"/>
       <c r="AQ2">
         <v>29</v>
       </c>
-      <c r="AR2"/>
       <c r="AS2">
         <v>30</v>
       </c>
-      <c r="AT2"/>
-    </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9760,7 +9376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -9900,7 +9516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -9911,7 +9527,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>0.4583333333333333</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -10040,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -10051,7 +9667,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10180,7 +9796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -10320,7 +9936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -10460,7 +10076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -10471,7 +10087,7 @@
         <v>92</v>
       </c>
       <c r="D9">
-        <v>0.5786163522012578</v>
+        <v>0.57861635220125784</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -10600,7 +10216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -10608,7 +10224,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -10616,18 +10232,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -10650,7 +10260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -10673,7 +10283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -10696,7 +10306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -10719,7 +10329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -10742,7 +10352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -10765,7 +10375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -10788,7 +10398,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -10811,7 +10421,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -10834,7 +10444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -10857,7 +10467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -10880,7 +10490,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -10903,7 +10513,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -10926,7 +10536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -10946,99 +10556,75 @@
         <v>274</v>
       </c>
     </row>
-    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30"/>
       <c r="G30">
         <v>2</v>
       </c>
-      <c r="H30"/>
       <c r="I30">
         <v>3</v>
       </c>
-      <c r="J30"/>
       <c r="K30">
         <v>5</v>
       </c>
-      <c r="L30"/>
       <c r="M30">
         <v>8</v>
       </c>
-      <c r="N30"/>
       <c r="O30">
         <v>9</v>
       </c>
-      <c r="P30"/>
       <c r="Q30">
         <v>10</v>
       </c>
-      <c r="R30"/>
       <c r="S30">
         <v>11</v>
       </c>
-      <c r="T30"/>
       <c r="U30">
         <v>12</v>
       </c>
-      <c r="V30"/>
       <c r="W30">
         <v>15</v>
       </c>
-      <c r="X30"/>
       <c r="Y30">
         <v>16</v>
       </c>
-      <c r="Z30"/>
       <c r="AA30">
         <v>17</v>
       </c>
-      <c r="AB30"/>
       <c r="AC30">
         <v>18</v>
       </c>
-      <c r="AD30"/>
       <c r="AE30">
         <v>19</v>
       </c>
-      <c r="AF30"/>
       <c r="AG30">
         <v>22</v>
       </c>
-      <c r="AH30"/>
       <c r="AI30">
         <v>23</v>
       </c>
-      <c r="AJ30"/>
       <c r="AK30">
         <v>24</v>
       </c>
-      <c r="AL30"/>
       <c r="AM30">
         <v>25</v>
       </c>
-      <c r="AN30"/>
       <c r="AO30">
         <v>26</v>
       </c>
-      <c r="AP30"/>
       <c r="AQ30">
         <v>29</v>
       </c>
-      <c r="AR30"/>
       <c r="AS30">
         <v>30</v>
       </c>
-      <c r="AT30"/>
-    </row>
-    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -11178,7 +10764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -11318,7 +10904,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -11458,7 +11044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -11598,7 +11184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -11609,7 +11195,7 @@
         <v>385</v>
       </c>
       <c r="D35">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E35">
         <v>17</v>
@@ -11738,7 +11324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -11878,7 +11464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -12019,95 +11605,31 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="AA30:AB30"/>
-    <mergeCell ref="AC30:AD30"/>
-    <mergeCell ref="AE30:AF30"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AI30:AJ30"/>
-    <mergeCell ref="AK30:AL30"/>
-    <mergeCell ref="AM30:AN30"/>
-    <mergeCell ref="AO30:AP30"/>
-    <mergeCell ref="AQ30:AR30"/>
-    <mergeCell ref="AS30:AT30"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:AK27"/>
-  <sheetFormatPr customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:AK25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:37" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
       <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
       <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="W2"/>
       <c r="AA2" t="s">
         <v>41</v>
       </c>
@@ -12133,7 +11655,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:37" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -12197,7 +11719,6 @@
       <c r="W3">
         <v>30</v>
       </c>
-      <c r="Y3"/>
       <c r="AA3">
         <v>1</v>
       </c>
@@ -12223,7 +11744,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -12318,7 +11839,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -12413,7 +11934,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -12511,7 +12032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:37" x14ac:dyDescent="0.3">
       <c r="AA7">
         <v>5</v>
       </c>
@@ -12537,7 +12058,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:37" x14ac:dyDescent="0.3">
       <c r="AA8">
         <v>6</v>
       </c>
@@ -12563,7 +12084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -12655,7 +12176,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -12735,7 +12256,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -12815,7 +12336,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -12898,7 +12419,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -12978,7 +12499,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -13058,7 +12579,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>72</v>
       </c>
@@ -13138,7 +12659,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
@@ -13218,7 +12739,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -13298,7 +12819,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -13378,7 +12899,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -13437,7 +12958,7 @@
         <v>17133.68</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -13493,7 +13014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -13561,7 +13082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -13632,7 +13153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -13703,7 +13224,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -13777,60 +13298,32 @@
         <v>-34</v>
       </c>
     </row>
-    <row r="27" spans="24:25" x14ac:dyDescent="0.25">
-      <c r="Y27"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X27:Y27"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:AH26"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
       <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
       <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="W2"/>
       <c r="AA2" t="s">
         <v>41</v>
       </c>
@@ -13856,7 +13349,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -13920,7 +13413,6 @@
       <c r="W3">
         <v>30</v>
       </c>
-      <c r="Y3"/>
       <c r="AA3">
         <v>1</v>
       </c>
@@ -13946,7 +13438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -14041,7 +13533,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -14136,7 +13628,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -14228,7 +13720,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA7">
         <v>5</v>
       </c>
@@ -14254,7 +13746,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA8">
         <v>6</v>
       </c>
@@ -14280,7 +13772,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -14372,7 +13864,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -14455,7 +13947,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -14538,7 +14030,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -14621,7 +14113,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -14704,7 +14196,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -14787,7 +14279,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>72</v>
       </c>
@@ -14870,7 +14362,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
@@ -14953,7 +14445,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -15036,7 +14528,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -15119,7 +14611,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -15202,7 +14694,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -15285,7 +14777,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -15377,7 +14869,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA22">
         <v>20</v>
       </c>
@@ -15403,7 +14895,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -15498,7 +14990,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -15593,7 +15085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -15667,63 +15159,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="24:31" x14ac:dyDescent="0.25">
-      <c r="Y26"/>
+    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AE26">
         <v>5231.58</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X26:Y26"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:AH26"/>
-  <sheetFormatPr customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B2:AH25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
       <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
       <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="W2"/>
       <c r="AA2" t="s">
         <v>41</v>
       </c>
@@ -15749,7 +15215,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -15813,7 +15279,6 @@
       <c r="W3">
         <v>30</v>
       </c>
-      <c r="Y3"/>
       <c r="AA3">
         <v>1</v>
       </c>
@@ -15827,7 +15292,7 @@
         <v>46148</v>
       </c>
       <c r="AE3">
-        <v>309.65</v>
+        <v>309.64999999999998</v>
       </c>
       <c r="AF3">
         <v>46175</v>
@@ -15839,7 +15304,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -15934,7 +15399,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -16029,7 +15494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -16127,7 +15592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA7">
         <v>5</v>
       </c>
@@ -16153,7 +15618,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA8">
         <v>7</v>
       </c>
@@ -16179,7 +15644,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -16271,7 +15736,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -16330,7 +15795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -16389,7 +15854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -16448,7 +15913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -16507,7 +15972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -16569,7 +16034,7 @@
         <v>1973.01</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>72</v>
       </c>
@@ -16628,7 +16093,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
@@ -16687,7 +16152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -16746,7 +16211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -16805,7 +16270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -16864,7 +16329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -16923,7 +16388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -16991,7 +16456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -17062,7 +16527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -17133,7 +16598,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -17204,60 +16669,32 @@
         <v>-38</v>
       </c>
     </row>
-    <row r="26" spans="24:25" x14ac:dyDescent="0.25">
-      <c r="Y26"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X26:Y26"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:AH30"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
       <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
       <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="W2"/>
       <c r="AA2" t="s">
         <v>41</v>
       </c>
@@ -17283,7 +16720,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -17347,7 +16784,6 @@
       <c r="W3">
         <v>30</v>
       </c>
-      <c r="Y3"/>
       <c r="AA3">
         <v>1</v>
       </c>
@@ -17373,7 +16809,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -17468,7 +16904,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -17563,7 +16999,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -17661,7 +17097,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA7">
         <v>5</v>
       </c>
@@ -17687,7 +17123,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA8">
         <v>6</v>
       </c>
@@ -17713,7 +17149,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -17805,7 +17241,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -17885,7 +17321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -17965,7 +17401,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -18045,7 +17481,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -18125,7 +17561,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -18205,7 +17641,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>72</v>
       </c>
@@ -18285,7 +17721,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
@@ -18365,7 +17801,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -18445,7 +17881,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -18525,7 +17961,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -18605,7 +18041,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -18685,7 +18121,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -18777,7 +18213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA22">
         <v>20</v>
       </c>
@@ -18803,7 +18239,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -18883,7 +18319,7 @@
         <v>46198</v>
       </c>
       <c r="AE23">
-        <v>631.2</v>
+        <v>631.20000000000005</v>
       </c>
       <c r="AF23">
         <v>44866</v>
@@ -18895,7 +18331,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -18990,7 +18426,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -19088,8 +18524,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="24:34" x14ac:dyDescent="0.25">
-      <c r="Y26"/>
+    <row r="26" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA26">
         <v>24</v>
       </c>
@@ -19115,7 +18550,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA27">
         <v>25</v>
       </c>
@@ -19141,7 +18576,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA28">
         <v>26</v>
       </c>
@@ -19167,7 +18602,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA29">
         <v>27</v>
       </c>
@@ -19193,62 +18628,37 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="31:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AE30">
         <v>19384</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X26:Y26"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:AH26"/>
-  <sheetFormatPr customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B2:AH25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
       <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
       <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
       <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
       <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="W2"/>
       <c r="AA2" t="s">
         <v>41</v>
       </c>
@@ -19274,7 +18684,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="3:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -19338,7 +18748,6 @@
       <c r="W3">
         <v>30</v>
       </c>
-      <c r="Y3"/>
       <c r="AA3">
         <v>1</v>
       </c>
@@ -19364,7 +18773,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>51</v>
       </c>
@@ -19459,7 +18868,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -19542,7 +18951,7 @@
         <v>46148</v>
       </c>
       <c r="AE5">
-        <v>533.7</v>
+        <v>533.70000000000005</v>
       </c>
       <c r="AF5">
         <v>46126</v>
@@ -19554,7 +18963,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -19649,7 +19058,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA7">
         <v>5</v>
       </c>
@@ -19675,7 +19084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA8">
         <v>6</v>
       </c>
@@ -19701,7 +19110,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -19793,7 +19202,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -19873,7 +19282,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -19953,7 +19362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>18</v>
       </c>
@@ -20033,7 +19442,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -20101,7 +19510,7 @@
         <v>46188</v>
       </c>
       <c r="AE13">
-        <v>275.35</v>
+        <v>275.35000000000002</v>
       </c>
       <c r="AF13">
         <v>46139</v>
@@ -20113,7 +19522,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -20193,7 +19602,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>72</v>
       </c>
@@ -20273,7 +19682,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>23</v>
       </c>
@@ -20353,7 +19762,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -20421,7 +19830,7 @@
         <v>46192</v>
       </c>
       <c r="AE17">
-        <v>265.15</v>
+        <v>265.14999999999998</v>
       </c>
       <c r="AF17">
         <v>46135</v>
@@ -20433,7 +19842,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -20513,7 +19922,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -20593,7 +20002,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -20673,7 +20082,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -20765,7 +20174,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="27:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:34" x14ac:dyDescent="0.3">
       <c r="AA22">
         <v>20</v>
       </c>
@@ -20791,7 +20200,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -20862,7 +20271,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -20933,7 +20342,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -21010,129 +20419,91 @@
         <v>13225.55</v>
       </c>
     </row>
-    <row r="26" spans="24:25" x14ac:dyDescent="0.25">
-      <c r="Y26"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:K2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="X26:Y26"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A2:AX38"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2"/>
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="H2"/>
       <c r="I2">
         <v>3</v>
       </c>
-      <c r="J2"/>
       <c r="K2">
         <v>6</v>
       </c>
-      <c r="L2"/>
       <c r="M2">
         <v>7</v>
       </c>
-      <c r="N2"/>
       <c r="O2">
         <v>8</v>
       </c>
-      <c r="P2"/>
       <c r="Q2">
         <v>9</v>
       </c>
-      <c r="R2"/>
       <c r="S2">
         <v>10</v>
       </c>
-      <c r="T2"/>
       <c r="U2">
         <v>13</v>
       </c>
-      <c r="V2"/>
       <c r="W2">
         <v>14</v>
       </c>
-      <c r="X2"/>
       <c r="Y2">
         <v>15</v>
       </c>
-      <c r="Z2"/>
       <c r="AA2">
         <v>16</v>
       </c>
-      <c r="AB2"/>
       <c r="AC2">
         <v>17</v>
       </c>
-      <c r="AD2"/>
       <c r="AE2">
         <v>20</v>
       </c>
-      <c r="AF2"/>
       <c r="AG2">
         <v>21</v>
       </c>
-      <c r="AH2"/>
       <c r="AI2">
         <v>22</v>
       </c>
-      <c r="AJ2"/>
       <c r="AK2">
         <v>23</v>
       </c>
-      <c r="AL2"/>
       <c r="AM2">
         <v>24</v>
       </c>
-      <c r="AN2"/>
       <c r="AO2">
         <v>27</v>
       </c>
-      <c r="AP2"/>
       <c r="AQ2">
         <v>28</v>
       </c>
-      <c r="AR2"/>
       <c r="AS2">
         <v>29</v>
       </c>
-      <c r="AT2"/>
       <c r="AU2">
         <v>30</v>
       </c>
-      <c r="AV2"/>
       <c r="AW2">
         <v>31</v>
       </c>
-      <c r="AX2"/>
-    </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -21284,7 +20655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -21412,7 +20783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>170</v>
       </c>
@@ -21543,7 +20914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -21671,7 +21042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>172</v>
       </c>
@@ -21802,7 +21173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -21939,7 +21310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -22091,7 +21462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -22100,7 +21471,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -22109,18 +21480,12 @@
         <v>-85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>174</v>
       </c>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -22146,7 +21511,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -22169,7 +21534,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -22192,7 +21557,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -22215,7 +21580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -22238,7 +21603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -22261,7 +21626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -22284,7 +21649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -22307,7 +21672,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -22330,7 +21695,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -22353,7 +21718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -22376,7 +21741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -22399,7 +21764,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -22422,7 +21787,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -22445,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -22465,107 +21830,81 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31"/>
       <c r="G31">
         <v>2</v>
       </c>
-      <c r="H31"/>
       <c r="I31">
         <v>3</v>
       </c>
-      <c r="J31"/>
       <c r="K31">
         <v>6</v>
       </c>
-      <c r="L31"/>
       <c r="M31">
         <v>7</v>
       </c>
-      <c r="N31"/>
       <c r="O31">
         <v>8</v>
       </c>
-      <c r="P31"/>
       <c r="Q31">
         <v>9</v>
       </c>
-      <c r="R31"/>
       <c r="S31">
         <v>10</v>
       </c>
-      <c r="T31"/>
       <c r="U31">
         <v>13</v>
       </c>
-      <c r="V31"/>
       <c r="W31">
         <v>14</v>
       </c>
-      <c r="X31"/>
       <c r="Y31">
         <v>15</v>
       </c>
-      <c r="Z31"/>
       <c r="AA31">
         <v>16</v>
       </c>
-      <c r="AB31"/>
       <c r="AC31">
         <v>17</v>
       </c>
-      <c r="AD31"/>
       <c r="AE31">
         <v>20</v>
       </c>
-      <c r="AF31"/>
       <c r="AG31">
         <v>21</v>
       </c>
-      <c r="AH31"/>
       <c r="AI31">
         <v>22</v>
       </c>
-      <c r="AJ31"/>
       <c r="AK31">
         <v>23</v>
       </c>
-      <c r="AL31"/>
       <c r="AM31">
         <v>24</v>
       </c>
-      <c r="AN31"/>
       <c r="AO31">
         <v>27</v>
       </c>
-      <c r="AP31"/>
       <c r="AQ31">
         <v>28</v>
       </c>
-      <c r="AR31"/>
       <c r="AS31">
         <v>29</v>
       </c>
-      <c r="AT31"/>
       <c r="AU31">
         <v>30</v>
       </c>
-      <c r="AV31"/>
       <c r="AW31">
         <v>31</v>
       </c>
-      <c r="AX31"/>
-    </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -22717,7 +22056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>169</v>
       </c>
@@ -22839,7 +22178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>170</v>
       </c>
@@ -22961,7 +22300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>171</v>
       </c>
@@ -23083,7 +22422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>172</v>
       </c>
@@ -23205,7 +22544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>173</v>
       </c>
@@ -23327,7 +22666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -23480,57 +22819,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="Y31:Z31"/>
-    <mergeCell ref="AA31:AB31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="AE31:AF31"/>
-    <mergeCell ref="AG31:AH31"/>
-    <mergeCell ref="AI31:AJ31"/>
-    <mergeCell ref="AK31:AL31"/>
-    <mergeCell ref="AM31:AN31"/>
-    <mergeCell ref="AO31:AP31"/>
-    <mergeCell ref="AQ31:AR31"/>
-    <mergeCell ref="AS31:AT31"/>
-    <mergeCell ref="AU31:AV31"/>
-    <mergeCell ref="AW31:AX31"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>